--- a/artfynd/A 51221-2022 artfynd.xlsx
+++ b/artfynd/A 51221-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115072907</v>
+        <v>114780622</v>
       </c>
       <c r="B2" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>1444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Berget (Rödene), Vg</t>
+          <t>Store-Tränsvägen 15, Rödene, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356075</v>
+        <v>356113</v>
       </c>
       <c r="R2" t="n">
-        <v>6427509</v>
+        <v>6427496</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,37 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115072888</v>
+        <v>89440061</v>
       </c>
       <c r="B3" t="n">
-        <v>57943</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,34 +817,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Berget (Rödene), Vg</t>
+          <t>Store-Tränsvägen 15, Rödene, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356116</v>
+        <v>356113</v>
       </c>
       <c r="R3" t="n">
-        <v>6427424</v>
+        <v>6427496</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nyligen (&gt; 15 min) påkörd på Store-Tränsvägen, söder om Store-Tränsvägen 15.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +891,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -928,53 +910,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115533821</v>
+        <v>115072907</v>
       </c>
       <c r="B4" t="n">
-        <v>103146</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Store-Tränsvägen 15 (Store-Tränsvägen 15), Vg</t>
+          <t>Östra Berget, Rödene, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>356080</v>
+        <v>356075</v>
       </c>
       <c r="R4" t="n">
-        <v>6427513</v>
+        <v>6427509</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +985,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,6 +1024,239 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115072888</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östra Berget, Rödene, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>356116</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6427424</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rödene</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Bergquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Bergquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115533821</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Store-Tränsvägen 15, Store-Tränsvägen 15, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>356080</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6427513</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rödene</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Bergquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Bergquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51221-2022 artfynd.xlsx
+++ b/artfynd/A 51221-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114780622</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89440061</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115072907</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115072888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,8 +1282,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115533821</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>